--- a/excel/Profitus Gerda.xlsx
+++ b/excel/Profitus Gerda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBFC474-FD01-4364-BAB7-164A90222A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ECA658-615E-4827-826B-65A6C9D5FA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="J3" s="9">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!B13</f>
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K3" s="9" t="str">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!S3</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>4.1886245965957656</v>
+        <v>3.3279531717300412</v>
       </c>
       <c r="AC3" s="9" t="str">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!AA2</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="J4" s="9">
         <f ca="1">'Druskonio Perlai, Druskininkai '!B13</f>
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K4" s="9" t="str">
         <f ca="1">'Druskonio Perlai, Druskininkai '!S3</f>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="L1" s="21">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>4.1886245965957656</v>
+        <v>3.3279531717300412</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3307,7 +3307,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="10">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>

--- a/excel/Profitus Gerda.xlsx
+++ b/excel/Profitus Gerda.xlsx
@@ -5,21 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Profitus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ECA658-615E-4827-826B-65A6C9D5FA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9E5008-FF55-43F4-B867-78D1DC764035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="12" r:id="rId2"/>
     <sheet name="Druskonio Perlai, Druskininkai " sheetId="24" r:id="rId3"/>
     <sheet name="Dvibučių kvartalas Kauno r. II" sheetId="20" r:id="rId4"/>
+    <sheet name="Sakurų Namai, Marijampolė III" sheetId="26" r:id="rId5"/>
+    <sheet name="Senvagės loftai, Panevėžys IV" sheetId="25" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="58">
   <si>
     <t>Paskola</t>
   </si>
@@ -202,6 +204,21 @@
   <si>
     <t>M</t>
   </si>
+  <si>
+    <t>Paskola P00001423-4</t>
+  </si>
+  <si>
+    <t>Senvagės loftai, Panevėžys IV</t>
+  </si>
+  <si>
+    <t>Paskola P00001405-3</t>
+  </si>
+  <si>
+    <t>Sakurų Namai, Marijampolė III</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
 </sst>
 </file>
 
@@ -345,7 +362,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -393,9 +410,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -406,19 +420,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -446,7 +448,63 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -514,13 +572,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -677,6 +728,118 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E9830A6-6DBD-44BF-A0D2-F6AC6284C5EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{718CB6D0-43AE-4EB8-BF6F-ACCD2760B4CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -686,6 +849,7 @@
     <sheetNames>
       <sheetName val="Overview"/>
       <sheetName val="Pinigai"/>
+      <sheetName val="Senvagės loftai, Panevėžys VIII"/>
       <sheetName val="Dvibučių kvartalas Kauno r. II"/>
       <sheetName val="Molėtų Oazė XII"/>
       <sheetName val="Europos 70, Kaunas XX"/>
@@ -710,21 +874,15 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
         <row r="2">
           <cell r="AA2" t="str">
             <v/>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="2">
           <cell r="AA2" t="str">
@@ -742,7 +900,7 @@
       <sheetData sheetId="8">
         <row r="2">
           <cell r="AA2" t="str">
-            <v/>
+            <v>+</v>
           </cell>
         </row>
       </sheetData>
@@ -781,13 +939,20 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="14">
+        <row r="2">
+          <cell r="AA2" t="str">
+            <v/>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1071,111 +1236,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31" t="s">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="O1" s="31" t="s">
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="O1" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="31"/>
-      <c r="U1" s="32" t="s">
+      <c r="T1" s="26"/>
+      <c r="U1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="24" t="s">
+      <c r="L2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="Q2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="24" t="s">
+      <c r="R2" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="T2" s="24" t="s">
+      <c r="S2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="U2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="24" t="s">
+      <c r="V2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="W2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="X2" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="AC2" s="23" t="s">
+      <c r="AC2" s="7" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1184,56 +1349,56 @@
         <v>1</v>
       </c>
       <c r="B3" s="10">
-        <f>'Dvibučių kvartalas Kauno r. II'!B3</f>
-        <v>46164</v>
+        <f>'Senvagės loftai, Panevėžys IV'!B3</f>
+        <v>45899</v>
       </c>
       <c r="C3" s="18" t="str">
-        <f>'Dvibučių kvartalas Kauno r. II'!B2</f>
-        <v>Dvibučių kvartalas Kauno r. II</v>
+        <f>'Senvagės loftai, Panevėžys IV'!B2</f>
+        <v>Senvagės loftai, Panevėžys IV</v>
       </c>
       <c r="D3" s="3">
-        <f>'Dvibučių kvartalas Kauno r. II'!B8</f>
+        <f>'Senvagės loftai, Panevėžys IV'!B8</f>
         <v>12</v>
       </c>
       <c r="E3" s="3" t="str">
-        <f>'Dvibučių kvartalas Kauno r. II'!B5</f>
+        <f>'Senvagės loftai, Panevėžys IV'!B5</f>
         <v>A</v>
       </c>
       <c r="F3" s="6">
-        <f>'Dvibučių kvartalas Kauno r. II'!B10</f>
-        <v>0.08</v>
+        <f>'Senvagės loftai, Panevėžys IV'!B10</f>
+        <v>0.09</v>
       </c>
       <c r="G3" s="5">
-        <f>'Dvibučių kvartalas Kauno r. II'!B11</f>
-        <v>106.3</v>
+        <f>'Senvagės loftai, Panevėžys IV'!B11</f>
+        <v>100</v>
       </c>
       <c r="H3" s="10">
-        <f>'Dvibučių kvartalas Kauno r. II'!B12</f>
-        <v>46531</v>
-      </c>
-      <c r="I3" s="10" t="str">
-        <f>'Dvibučių kvartalas Kauno r. II'!R3</f>
-        <v/>
-      </c>
-      <c r="J3" s="9">
-        <f ca="1">'Dvibučių kvartalas Kauno r. II'!B13</f>
-        <v>291</v>
+        <f>'Senvagės loftai, Panevėžys IV'!B12</f>
+        <v>46264</v>
+      </c>
+      <c r="I3" s="10">
+        <f>'Senvagės loftai, Panevėžys IV'!R3</f>
+        <v>46248</v>
+      </c>
+      <c r="J3" s="9" t="str">
+        <f ca="1">'Senvagės loftai, Panevėžys IV'!B13</f>
+        <v/>
       </c>
       <c r="K3" s="9" t="str">
-        <f ca="1">'Dvibučių kvartalas Kauno r. II'!S3</f>
+        <f ca="1">'Senvagės loftai, Panevėžys IV'!S3</f>
         <v/>
       </c>
       <c r="L3" s="5">
-        <f>'Dvibučių kvartalas Kauno r. II'!N3</f>
-        <v>0</v>
+        <f>'Senvagės loftai, Panevėžys IV'!N3</f>
+        <v>100</v>
       </c>
       <c r="M3" s="5">
-        <f>'Dvibučių kvartalas Kauno r. II'!P3</f>
-        <v>0</v>
+        <f>'Senvagės loftai, Panevėžys IV'!P3</f>
+        <v>8.56</v>
       </c>
       <c r="O3" s="5">
         <f>Pinigai!I2</f>
-        <v>215.3</v>
+        <v>200.31</v>
       </c>
       <c r="P3" s="5">
         <f>SUM(G3:G200)-S3</f>
@@ -1245,34 +1410,34 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>0</v>
+        <v>2.2599999999999909</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>240.3</v>
+        <v>242.56</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>25</v>
+        <v>42.25</v>
       </c>
       <c r="W3" s="14">
         <f>(U3-O3)/O3</f>
-        <v>0.1161170459823502</v>
+        <v>0.21092306924267384</v>
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>3.3279531717300412</v>
-      </c>
-      <c r="AC3" s="9" t="str">
-        <f ca="1">'Dvibučių kvartalas Kauno r. II'!AA2</f>
+        <v>0.20990729928016669</v>
+      </c>
+      <c r="AC3" s="5" t="str">
+        <f ca="1">'Senvagės loftai, Panevėžys IV'!AA2</f>
         <v/>
       </c>
     </row>
@@ -1281,55 +1446,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="10">
-        <f>'Druskonio Perlai, Druskininkai '!B3</f>
-        <v>46192</v>
+        <f>'Sakurų Namai, Marijampolė III'!B3</f>
+        <v>45899</v>
       </c>
       <c r="C4" s="18" t="str">
-        <f>'Druskonio Perlai, Druskininkai '!B2</f>
-        <v>Druskonio Perlai, Druskininkai XV</v>
+        <f>'Sakurų Namai, Marijampolė III'!B2</f>
+        <v>Sakurų Namai, Marijampolė III</v>
       </c>
       <c r="D4" s="3">
-        <f>'Druskonio Perlai, Druskininkai '!B8</f>
+        <f>'Sakurų Namai, Marijampolė III'!B8</f>
         <v>12</v>
       </c>
       <c r="E4" s="3" t="str">
-        <f>'Druskonio Perlai, Druskininkai '!B5</f>
-        <v>A</v>
+        <f>'Sakurų Namai, Marijampolė III'!B5</f>
+        <v>A-</v>
       </c>
       <c r="F4" s="6">
-        <f>'Druskonio Perlai, Druskininkai '!B10</f>
-        <v>8.4000000000000005E-2</v>
+        <f>'Sakurų Namai, Marijampolė III'!B10</f>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="G4" s="5">
-        <f>'Druskonio Perlai, Druskininkai '!B11</f>
-        <v>134</v>
+        <f>'Sakurų Namai, Marijampolė III'!B11</f>
+        <v>100</v>
       </c>
       <c r="H4" s="10">
-        <f>'Druskonio Perlai, Druskininkai '!B12</f>
-        <v>46559</v>
-      </c>
-      <c r="I4" s="10" t="str">
-        <f>'Druskonio Perlai, Druskininkai '!R3</f>
-        <v/>
-      </c>
-      <c r="J4" s="9">
-        <f ca="1">'Druskonio Perlai, Druskininkai '!B13</f>
-        <v>319</v>
+        <f>'Sakurų Namai, Marijampolė III'!B12</f>
+        <v>46265</v>
+      </c>
+      <c r="I4" s="10">
+        <f>'Sakurų Namai, Marijampolė III'!R3</f>
+        <v>46154</v>
+      </c>
+      <c r="J4" s="9" t="str">
+        <f ca="1">'Sakurų Namai, Marijampolė III'!B13</f>
+        <v/>
       </c>
       <c r="K4" s="9" t="str">
-        <f ca="1">'Druskonio Perlai, Druskininkai '!S3</f>
+        <f ca="1">'Sakurų Namai, Marijampolė III'!S3</f>
         <v/>
       </c>
       <c r="L4" s="5">
-        <f>'Druskonio Perlai, Druskininkai '!N3</f>
-        <v>0</v>
+        <f>'Sakurų Namai, Marijampolė III'!N3</f>
+        <v>100</v>
       </c>
       <c r="M4" s="5">
-        <f>'Druskonio Perlai, Druskininkai '!P3</f>
-        <v>0</v>
+        <f>'Sakurų Namai, Marijampolė III'!P3</f>
+        <v>6.43</v>
       </c>
       <c r="AC4" s="5" t="str">
-        <f ca="1">'Druskonio Perlai, Druskininkai '!AA2</f>
+        <f ca="1">'Sakurų Namai, Marijampolė III'!AA2</f>
         <v/>
       </c>
     </row>
@@ -1337,18 +1502,54 @@
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="B5" s="10">
+        <f>'Dvibučių kvartalas Kauno r. II'!B3</f>
+        <v>46164</v>
+      </c>
+      <c r="C5" s="18" t="str">
+        <f>'Dvibučių kvartalas Kauno r. II'!B2</f>
+        <v>Dvibučių kvartalas Kauno r. II</v>
+      </c>
+      <c r="D5" s="3">
+        <f>'Dvibučių kvartalas Kauno r. II'!B8</f>
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <f>'Dvibučių kvartalas Kauno r. II'!B5</f>
+        <v>A</v>
+      </c>
+      <c r="F5" s="6">
+        <f>'Dvibučių kvartalas Kauno r. II'!B10</f>
+        <v>0.08</v>
+      </c>
+      <c r="G5" s="5">
+        <f>'Dvibučių kvartalas Kauno r. II'!B11</f>
+        <v>106.3</v>
+      </c>
+      <c r="H5" s="10">
+        <f>'Dvibučių kvartalas Kauno r. II'!B12</f>
+        <v>46531</v>
+      </c>
+      <c r="I5" s="10" t="str">
+        <f>'Dvibučių kvartalas Kauno r. II'!R3</f>
+        <v/>
+      </c>
+      <c r="J5" s="9">
+        <f ca="1">'Dvibučių kvartalas Kauno r. II'!B13</f>
+        <v>265</v>
+      </c>
+      <c r="K5" s="9" t="str">
+        <f ca="1">'Dvibučių kvartalas Kauno r. II'!S3</f>
+        <v/>
+      </c>
+      <c r="L5" s="5">
+        <f>'Dvibučių kvartalas Kauno r. II'!N3</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <f>'Dvibučių kvartalas Kauno r. II'!P3</f>
+        <v>2.2599999999999998</v>
+      </c>
       <c r="AC5" s="5" t="str">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!AA2</f>
         <v/>
@@ -1358,19 +1559,58 @@
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="AC6" s="9"/>
+      <c r="B6" s="10">
+        <f>'Druskonio Perlai, Druskininkai '!B3</f>
+        <v>46192</v>
+      </c>
+      <c r="C6" s="18" t="str">
+        <f>'Druskonio Perlai, Druskininkai '!B2</f>
+        <v>Druskonio Perlai, Druskininkai XV</v>
+      </c>
+      <c r="D6" s="3">
+        <f>'Druskonio Perlai, Druskininkai '!B8</f>
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="str">
+        <f>'Druskonio Perlai, Druskininkai '!B5</f>
+        <v>A</v>
+      </c>
+      <c r="F6" s="6">
+        <f>'Druskonio Perlai, Druskininkai '!B10</f>
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="G6" s="5">
+        <f>'Druskonio Perlai, Druskininkai '!B11</f>
+        <v>134</v>
+      </c>
+      <c r="H6" s="10">
+        <f>'Druskonio Perlai, Druskininkai '!B12</f>
+        <v>46559</v>
+      </c>
+      <c r="I6" s="10" t="str">
+        <f>'Druskonio Perlai, Druskininkai '!R3</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f ca="1">'Druskonio Perlai, Druskininkai '!B13</f>
+        <v>293</v>
+      </c>
+      <c r="K6" s="9" t="str">
+        <f ca="1">'Druskonio Perlai, Druskininkai '!S3</f>
+        <v/>
+      </c>
+      <c r="L6" s="5">
+        <f>'Druskonio Perlai, Druskininkai '!N3</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <f>'Druskonio Perlai, Druskininkai '!P3</f>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="5" t="str">
+        <f ca="1">'Druskonio Perlai, Druskininkai '!AA2</f>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1442,10 +1682,7 @@
       <c r="K10" s="9"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="AC10" s="9" t="str">
-        <f>'[1]Dvibutis Upės g.'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC10" s="9"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -1463,10 +1700,7 @@
       <c r="K11" s="9"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
-      <c r="AC11" s="9" t="str">
-        <f>'[1]Dvibutis Klevų g.'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC11" s="9"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -1484,10 +1718,7 @@
       <c r="K12" s="9"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
-      <c r="AC12" s="9" t="str">
-        <f>'[1]Dvibutis Upelio g., Vilniaus r.'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC12" s="9"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -1505,10 +1736,7 @@
       <c r="K13" s="9"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
-      <c r="AC13" s="9" t="str">
-        <f>'[1]Piekrasta Rezidence, Ryga XII'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC13" s="9"/>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -1526,10 +1754,7 @@
       <c r="K14" s="9"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="AC14" s="9" t="str">
-        <f>'[1]Dvibutis Didžiojoje Riešėje'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC14" s="9"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -1547,10 +1772,7 @@
       <c r="K15" s="9"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
-      <c r="AC15" s="9" t="str">
-        <f>'[1]Sklypas Kalnėnuose, Vilnius II'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC15" s="9"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -1568,10 +1790,7 @@
       <c r="K16" s="9"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-      <c r="AC16" s="9" t="str">
-        <f>'[1]Golf Hills Vilos, Alikantė'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC16" s="9"/>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -1780,45 +1999,37 @@
     <mergeCell ref="U1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:M27">
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="21" priority="5">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="20" priority="6">
       <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>$AC4="+"</formula>
+  <conditionalFormatting sqref="AC3:AC6">
+    <cfRule type="expression" dxfId="19" priority="1">
+      <formula>$AC3="+"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC5">
-    <cfRule type="expression" dxfId="11" priority="2">
-      <formula>AND($G4&gt;0,$G4=$L4)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC5">
-    <cfRule type="expression" dxfId="10" priority="6">
-      <formula>#REF!="+"</formula>
+    <cfRule type="expression" dxfId="18" priority="2">
+      <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC20">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="17" priority="11">
       <formula>AND($G20&gt;0,$G20=$L20)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="16" priority="12">
       <formula>$AC20="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C3" location="'Dvibučių kvartalas Kauno r. II'!A1" display="'Dvibučių kvartalas Kauno r. II'!A1" xr:uid="{3E728898-2FEE-4453-AB81-EB1EF1C9F75D}"/>
-    <hyperlink ref="C4" location="'Druskonio Perlai, Druskininkai '!A1" display="'Druskonio Perlai, Druskininkai '!A1" xr:uid="{B8A89C1E-CA8F-4F58-BCA9-D3EE30D9BB60}"/>
+    <hyperlink ref="C3" location="'Senvagės loftai, Panevėžys IV'!A1" display="'Senvagės loftai, Panevėžys IV'!A1" xr:uid="{3E728898-2FEE-4453-AB81-EB1EF1C9F75D}"/>
+    <hyperlink ref="C4" location="'Sakurų Namai, Marijampolė III'!A1" display="'Sakurų Namai, Marijampolė III'!A1" xr:uid="{B8A89C1E-CA8F-4F58-BCA9-D3EE30D9BB60}"/>
+    <hyperlink ref="C5" location="'Dvibučių kvartalas Kauno r. II'!A1" display="'Dvibučių kvartalas Kauno r. II'!A1" xr:uid="{5BFE923A-0E21-4F30-8CD6-122789B6DF6F}"/>
+    <hyperlink ref="C6" location="'Druskonio Perlai, Druskininkai '!A1" display="'Druskonio Perlai, Druskininkai '!A1" xr:uid="{D0E87783-F841-4E1B-9D33-B5ADACD93D28}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="AC4" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1827,7 +2038,7 @@
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="20" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="19" customWidth="1"/>
     <col min="2" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" customWidth="1"/>
     <col min="6" max="9" width="10.7109375" customWidth="1"/>
@@ -1860,20 +2071,20 @@
       <c r="I1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="21">
+      <c r="L1" s="20">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>3.3279531717300412</v>
+        <v>0.20990729928016669</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
-        <v>46156</v>
+        <v>45899</v>
       </c>
       <c r="B2" s="5">
-        <v>106.34</v>
+        <v>200</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
@@ -1883,7 +2094,7 @@
       </c>
       <c r="F2" s="5">
         <f>SUM(B2:B36)</f>
-        <v>215.3</v>
+        <v>200.31</v>
       </c>
       <c r="G2" s="5">
         <f>SUM(C2:C36)</f>
@@ -1895,70 +2106,58 @@
       </c>
       <c r="I2" s="5">
         <f>F2-G2</f>
-        <v>215.3</v>
+        <v>200.31</v>
       </c>
       <c r="K2" s="5">
         <f>B2*-1</f>
-        <v>-106.34</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
-        <v>46284</v>
-      </c>
-      <c r="B3" s="27">
-        <v>108.96</v>
-      </c>
-      <c r="C3" s="27">
-        <v>0</v>
-      </c>
-      <c r="D3" s="27">
+      <c r="A3" s="10">
+        <v>46171</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
         <v>25</v>
       </c>
       <c r="K3" s="5">
-        <f t="shared" ref="K3:K7" si="0">B3*-1</f>
-        <v>-108.96</v>
+        <f t="shared" ref="K3" si="0">B3*-1</f>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="K4" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A4" s="10"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="K5" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A5" s="10"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="K6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A6" s="10"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="K7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
@@ -3307,14 +3506,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="10">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="5">
         <f>Overview!U3</f>
-        <v>240.3</v>
+        <v>242.56</v>
       </c>
     </row>
   </sheetData>
@@ -3348,22 +3547,22 @@
       <c r="B1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="25" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -3372,30 +3571,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="25"/>
+      <c r="O1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="25"/>
+      <c r="Q1" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="28" t="s">
         <v>39</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="25" t="s">
+      <c r="Z1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" s="25" t="s">
+      <c r="AA1" s="7" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3429,15 +3628,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46192</v>
@@ -3773,7 +3972,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -3800,7 +3999,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="25"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -3828,7 +4027,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="25"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -3849,7 +4048,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="25"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -3870,7 +4069,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="25"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -3891,7 +4090,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="25"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -3912,7 +4111,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="25"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -3933,7 +4132,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="25"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -3954,7 +4153,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="25"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -3975,7 +4174,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="25"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -3996,7 +4195,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="25"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -4017,7 +4216,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="25"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -4038,7 +4237,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="25"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -4059,7 +4258,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="25"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -4080,7 +4279,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="25"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -4101,7 +4300,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="25"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -4122,7 +4321,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="25"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -4143,7 +4342,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="25"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -4164,7 +4363,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="25"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -4185,7 +4384,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="25"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -4206,7 +4405,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="25"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -4227,7 +4426,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="25"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -4248,7 +4447,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="25"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -4269,7 +4468,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="25"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -4290,7 +4489,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="25"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -4311,7 +4510,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="25"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -4332,7 +4531,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="25"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -4353,7 +4552,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="25"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -4374,7 +4573,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="25"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -4395,7 +4594,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -4430,20 +4629,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4477,22 +4676,22 @@
       <c r="B1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="23" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="23" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -4501,30 +4700,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="25"/>
+      <c r="O1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="25"/>
+      <c r="Q1" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="28" t="s">
         <v>39</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="23" t="s">
+      <c r="Z1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" s="23" t="s">
+      <c r="AA1" s="7" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4544,13 +4743,21 @@
       <c r="F2" s="5">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="9" t="str">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46265</v>
+      </c>
+      <c r="K2" s="9">
         <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>31</v>
@@ -4558,15 +4765,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46164</v>
@@ -4618,7 +4825,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -4634,11 +4841,11 @@
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Z3" s="5">
         <f>G2+H2+I2</f>
-        <v>0</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -4902,7 +5109,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -4929,7 +5136,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -4957,7 +5164,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="23"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -4978,7 +5185,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="23"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -4999,7 +5206,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="23"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -5020,7 +5227,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="23"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -5041,7 +5248,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="23"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -5062,7 +5269,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="23"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -5083,7 +5290,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="23"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -5104,7 +5311,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="23"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -5125,7 +5332,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="23"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -5146,7 +5353,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="23"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -5167,7 +5374,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="23"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -5188,7 +5395,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="23"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -5209,7 +5416,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="23"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -5230,7 +5437,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="23"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -5251,7 +5458,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="23"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -5272,7 +5479,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="23"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -5293,7 +5500,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="23"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -5314,7 +5521,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="23"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -5335,7 +5542,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="23"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -5356,7 +5563,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="23"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -5377,7 +5584,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="23"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -5398,7 +5605,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="23"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -5419,7 +5626,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="23"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -5440,7 +5647,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="23"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -5461,7 +5668,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="23"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -5482,7 +5689,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="23"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -5503,7 +5710,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="23"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -5524,7 +5731,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -5541,7 +5748,2339 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="8" priority="16">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32FA4F6C-666D-4AD9-8D2F-6BABFBB5F4FB}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="25"/>
+      <c r="O1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46022</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3.13</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>3.13</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46022</v>
+      </c>
+      <c r="K2" s="9">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="Y2" s="10">
+        <f>B3</f>
+        <v>45899</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>B11*-1</f>
+        <v>-100</v>
+      </c>
+      <c r="AA2" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="10">
+        <v>45899</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46112</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.34</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2.34</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>46113</v>
+      </c>
+      <c r="K3" s="9">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <f>B11</f>
+        <v>100</v>
+      </c>
+      <c r="N3" s="5">
+        <f>G42</f>
+        <v>100</v>
+      </c>
+      <c r="O3" s="5">
+        <f>F42</f>
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="P3" s="5">
+        <f>H42+I42</f>
+        <v>6.43</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
+        <v>9.5190784335136405E-2</v>
+      </c>
+      <c r="R3" s="10">
+        <f>IF(M3=N3,B14,"")</f>
+        <v>46154</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="10">
+        <f>J2</f>
+        <v>46022</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>G2+H2+I2</f>
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="10">
+        <v>45902</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46203</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.37</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10">
+        <v>46154</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="0"/>
+        <v>-49</v>
+      </c>
+      <c r="Y4" s="10">
+        <f t="shared" ref="Y4:Y41" si="1">J3</f>
+        <v>46113</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" ref="Z4:Z41" si="2">G3+H3+I3</f>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="10">
+        <v>46265</v>
+      </c>
+      <c r="E5" s="5">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.61</v>
+      </c>
+      <c r="G5" s="5">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>46154</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>-111</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="1"/>
+        <v>46154</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="10">
+        <f t="shared" si="1"/>
+        <v>46154</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="2"/>
+        <v>100.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="5">
+        <v>100</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46265</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="9" t="str">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46154</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="3">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v>-111</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="7"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y16" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D17" s="7"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D18" s="7"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D19" s="7"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D20" s="7"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D21" s="7"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D23" s="7"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y23" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D26" s="7"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D27" s="7"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D28" s="7"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D29" s="7"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y29" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D30" s="7"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D31" s="7"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D32" s="7"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D33" s="7"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D34" s="7"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D35" s="7"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D36" s="7"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D37" s="7"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D38" s="7"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y38" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D39" s="7"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D40" s="7"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D41" s="7"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y41" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D42" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E2:E41)</f>
+        <v>100</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="3"/>
+        <v>6.43</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{060D4ADA-F7AF-4F3A-8FB9-FA4D5FEA4428}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="25"/>
+      <c r="O1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46022</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46022</v>
+      </c>
+      <c r="K2" s="9">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="Y2" s="10">
+        <f>B3</f>
+        <v>45899</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>B11*-1</f>
+        <v>-100</v>
+      </c>
+      <c r="AA2" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="10">
+        <v>45899</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46112</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K3" s="9">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <f>B11</f>
+        <v>100</v>
+      </c>
+      <c r="N3" s="5">
+        <f>G42</f>
+        <v>100</v>
+      </c>
+      <c r="O3" s="5">
+        <f>F42</f>
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="P3" s="5">
+        <f>H42+I42</f>
+        <v>8.56</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
+        <v>9.2495992779731764E-2</v>
+      </c>
+      <c r="R3" s="10">
+        <f>IF(M3=N3,B14,"")</f>
+        <v>46248</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="10">
+        <f>J2</f>
+        <v>46022</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>G2+H2+I2</f>
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="10">
+        <v>45901</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46203</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10">
+        <v>46204</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y4" s="10">
+        <f t="shared" ref="Y4:Y41" si="1">J3</f>
+        <v>46112</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" ref="Z4:Z41" si="2">G3+H3+I3</f>
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10">
+        <v>46264</v>
+      </c>
+      <c r="E5" s="5">
+        <v>100</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>46248</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>-16</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="1"/>
+        <v>46204</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.59</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="10">
+        <f t="shared" si="1"/>
+        <v>46248</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="2"/>
+        <v>101.11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="5">
+        <v>100</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46264</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="9" t="str">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46248</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="3">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v>-16</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="7"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y16" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D17" s="7"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D18" s="7"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D19" s="7"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D20" s="7"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D21" s="7"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D23" s="7"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y23" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D26" s="7"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D27" s="7"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D28" s="7"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D29" s="7"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y29" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D30" s="7"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D31" s="7"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D32" s="7"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D33" s="7"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D34" s="7"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D35" s="7"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D36" s="7"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D37" s="7"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D38" s="7"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y38" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D39" s="7"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D40" s="7"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D41" s="7"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y41" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D42" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E2:E41)</f>
+        <v>100</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="3"/>
+        <v>8.56</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
@@ -5567,12 +8106,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="1" priority="15">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
